--- a/borchestra_enemies.xlsx
+++ b/borchestra_enemies.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,6 +428,750 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ImpenetrableAngler_EN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Impenetrable Angler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>YellowSandbank_EN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Yellow Sandbank</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sandbank_EN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sandbank</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GoldRoadie_EN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Gold Roadie</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Roadie_EN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Roadie</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SterileBud_EN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sterile Bud</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chapbull_EN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Chapbull</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chapman_EN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Chapman</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cherubim_EN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Cherubim</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CopperCougher_EN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Copper Cougher</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DavyFlarb_EN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Davy Flarb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DyingFlarb_EN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Dying Flarb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GrippingTentacle_EN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Gripping Tentacle</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SqueezingTentacle_EN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Squeezing Tentacle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CarefulTentacle_EN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Careful Tentacle</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DesperateTentacle_EN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Desperate Tentacle</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DepressionSquid_BOSS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Depression Squid</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Doula_BOSS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Doula</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Deer_EN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Deer</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Stag_EN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Stag</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DrySimian_EN</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Dry Simian</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Flarbleft_EN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Flarbleft</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TheFountainofYouth_EN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>The Fountain of Youth</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NakedGizo_EN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gizo</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Gizo_EN</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gizo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TheGoblin_EN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Goblin</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DesiccatingJumbleguts_EN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Desiccating Jumbleguts</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PerforatedSpoggle_EN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Perforated Spoggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HeinousHighness_EN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Heinous Highness</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RockSelfish_EN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Selfish Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RockTrapping_EN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trapping Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RockPouring_EN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Pouring Rock</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Intijar_BOSS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Intijar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kekapex_EN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kekapex</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ConductorEnemy_EN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Conductor</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OneManBandEnemy_EN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>One Man Band</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Lipbug_EN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lipbug</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Maestro_EN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Maestro</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Metatron_EN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Metatron</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Neoplasm_EN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Neoplasm</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NeoplasmHeap_EN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Neoplasm Heap</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NeoplasmLake_EN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Neoplasm Lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nephilim_EN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nephilim</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FamiliarSpoggle_EN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Familiar Spoggle</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ophanim_EN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ophanim</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Opisthotonus_EN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Opisthotonus</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TitteringPeon_EN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Tittering Peon</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Psychopomp_EN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Psychopomp</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Revolie_EN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Revolie</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RevoltingRevola_EN</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Revolting Revola</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sachiel_EN</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Sachiel</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ScreamingHomunculus_EN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Screaming Homunculus</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Seraphim_EN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Seraphim</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SingingMountain_EN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Singing Mountain</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unflarb_EN</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unflarb</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HumanElemental_EN</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Human Element</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MalformedUnicorn_BOSS</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Malformed Unicorn</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unterling_EN</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unterling</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GigglingUsurper_EN</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Giggling Usurper</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Vermin_EN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Vermin</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WetSimian_EN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Wet Simian</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BastardZygote_EN</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Bastard Zygote</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
